--- a/data/worldcup_0623_0623update.xlsx
+++ b/data/worldcup_0623_0623update.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -455,98 +455,206 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>世体：约旦对阵阿尔及利亚，J组生死战</t>
+          <t>Who are the ITV commentators, pundits and presenters for Jordan vs Algeria?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-22 14:33</t>
+          <t>Tue, 23 Jun 2026 01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956962.html</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>https://www.fourfourtwo.com/competition/who-are-the-itv-commentators-pundits-and-presenters-for-jordan-vs-algeria</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>The ITV commentators, pundits and presenters for Jordan’s World Cup 2026 clash with Algeria have been revealed.  World Cup debutants Jordan fell to de</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jordan vs Algeria Prediction: World Cup 2026 Match Preview</t>
+          <t>How to watch Jordan vs Algeria for FREE: Live stream details for World Cup 2026 clash</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-21T09:10:33</t>
+          <t>Tue, 23 Jun 2026 01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/jordan-vs-algeria-prediction-world-cup-2026-match-preview/</t>
+          <t>https://www.fourfourtwo.com/competition/watch-jordan-vs-algeria-for-free-world-cup-2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Who will get their first points in Group J of the 2026 World Cup ? We look ahead to Tuesday’s clash in San Francisco with our Jordan vs Algeria predic</t>
+          <t>Jordan and Algeria each fell to defeats in their opening Group J fixtures of World Cup 2026 and both sides know that another loss would virtually spel</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>官方：斯洛文尼亚裁判温契奇将执法世界杯约旦vs阿尔及利亚</t>
+          <t>Jordan vs Algeria prediction: Will World Cup debutants claim their first win?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-19 20:53</t>
+          <t>Tue, 23 Jun 2026 00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5949678.html</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>https://www.fourfourtwo.com/competition/jordan-vs-algeria-prediction-will-world-cup-debutants-claim-their-first-win</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Having seen fellow debutants Cape Verde and Curacao grab the headlines over the weekend, now is the time for Jordan to announce themselves at World Cu</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Jordan v Algeria: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tue Jun 23 2026 01:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/23/fifa-world-cup-2026-live-jordan-v-algeria-updates-jor-v-alg-group-j-match-score-latest</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>⚽️ Kick-off time: 8pm local/1pm AEST/4am BST/11pm EDT ⚽️ Player guide | Bracketology | Golden Boot | Mail Martin  Earlier today, Messi’s Argentina met</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>世体：约旦对阵阿尔及利亚，J组生死战</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:33</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956962.html</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jordan vs Algeria Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-21T09:10:33</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/jordan-vs-algeria-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Who will get their first points in Group J of the 2026 World Cup ? We look ahead to Tuesday’s clash in San Francisco with our Jordan vs Algeria predic</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>官方：斯洛文尼亚裁判温契奇将执法世界杯约旦vs阿尔及利亚</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-19 20:53</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5949678.html</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Jordan vs Algeria: predictions, best bets, odds and stats</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>1 hour ago</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/jordan-vs-algeria-predictions-tips-23-06-26/</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">No previous meetings between these teams.
 No price boosts for this event.
@@ -556,193 +664,374 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>约旦vs阿尔及利亚：塔马里PK马赫雷斯，马扎、艾特-努里首发</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959209&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>'There is something up with that football' Joe Hart reveals World Cup Trionda theory behind strange Kylian Mbappe and Lionel Messi phenomenon</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/there-is-something-up-with-that-football-joe-hart-reveals-world-cup-trionda-theory-behind-strange-kylian-mbappe-and-lionel-messi-phenomenon</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>It wouldn't a World Cup unless there were goalkeepers complaining about the flight of the ball.  Kylian Mbappe's opener for France against Iraq on Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lionel Messi: Argentina star breaks World Cup scoring record with goal against Austria at 2026 World Cup</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 18</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/news/12040/13556817/lionel-messi-argentina-star-breaks-world-cup-scoring-record-with-goal-against-austria-at-2026-world-cup</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Lionel Messi has broken Miroslav Klose's record as the all-time leading goalscorer at a World Cup; the Argentina star scored a hat-trick against Alger</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Who is the referee for Argentina vs Austria?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 16</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-is-the-referee-for-argentina-vs-austria</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Argentina and Austria both started their World Cup campaigns with wins, beating Algeria and Jordan respectively.  The two go head-to-head this evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>How to watch Argentina vs Austria for FREE: Live stream details for Lionel Messi's record attempt at World Cup 2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 15</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-argentina-vs-austria-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lionel Messi's hat-trick in Argentina's first match at World Cup 2026 took him level with German striker Miroslav Klose as the record scorer at men's </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Who are the BBC commentators, pundits and presenters for Argentina vs Austria?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/bbc-commentators-pundits-presenters-argentina-vs-austria</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The BBC commentators, pundits and presenters for Argentina’s World Cup 2026 clash with Austria have been revealed.  The reigning champions made the pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Messi and Argentina ready to turn up the heat after fast World Cup start</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>guardian</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 02</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://www.theguardian.com/football/2026/jun/22/lionel-messi-argentina-austria-world-cup</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">It is the 40th anniversary of Diego Maradona’s exploits against England. The scene is set for Lionel Messi to imbue the date with fresh significance  </t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Squawka’s World Cup AI Predictor: AI score predictions for Monday June 22 at the 2026 World Cup</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>9 hours ago</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/squawkas-world-cup-ai-predictor-22-06/</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Using data from previous tournaments and qualifying, we’ve tasked our model with creating some World Cup AI predictions with correct score picks on ev</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria; FIFA World Cup Group J</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6:00pm, Monday 22nd</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/argentina-vs-austria/report/549808</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Argentina                           vs Austria. FIFA World Cup Group J.  6:00pm, Monday 22nd June 2026.  Dallas Stadium Attendance: Attendance 70,649.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>不虚此行！新军佛得角、库拉索、约旦、乌兹均取得世界杯首球</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>2026-06-22 06:32</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956261</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>2026年美加墨世界杯扩军至48支球队，佛得角、库拉索、约旦、乌兹别克斯坦成为了本届世界杯的四支新军。在佛得角队取得历史性首球后，本届世界杯的四支新军都已经取得进球，其中佛得角和库拉索还实现了拿一分的目标。
 佛得角世界杯首秀0-0逼平西班牙，就已经足够令人震惊，他们又在与乌拉圭的比赛中由凯文-皮纳</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Slick Spain shine as Sharks shock the Celeste</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>2026-06-21T22:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/matchday-11-round-up-review-highlights</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Lamine Yamal got Spain scoring at the FIFA World Cup 2026™ but it was Cabo Verde who once again stole the show with a 2-2 draw against Uruguay.
 Spain</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Argentina vs Austria Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>2026-06-21T09:34:56</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/argentina-vs-austria-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Can Austria stop Lionel Messi making FIFA World Cup history and securing another win for Argentina? We look ahead to the game with our Argentina vs Au</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Argentina and France among quartet eyeing knockout stage</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>2026-06-21T09:00:00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/preview-matchday-twelve</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Find out all the key details as Groups I and J return to action at FIFA World Cup 2026, headlined by former winners Argentina and France.
 Argentina m</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Argentina vs Austria: predictions, best bets, stats &amp; odds</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>1 hour ago</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/argentina-vs-austria-predictions-betting-tips-22-06-26/</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">No previous meetings between these teams.
 No price boosts for this event.
@@ -752,234 +1041,388 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Jordan at the World Cup 2026: Team Guide — History, Style, Players &amp; Group J</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>kickoff</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://kickoff.guide/blog/jordan-world-cup-2026-guide</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>A team profile of Jordan (Al-Nashama), who reached a first-ever FIFA World Cup: 63rd in the FIFA ranking, 2023 Asian Cup runners-up, Jamal Sellami's t</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Algeria at the World Cup 2026: Team Guide — History, Style, Players &amp; Group J</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>kickoff</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://kickoff.guide/blog/algeria-world-cup-2026-guide</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>A team profile of Algeria (Desert Foxes), back at the FIFA World Cup after 12 years: 35th in the FIFA ranking, 5th appearance, best result Round of 16</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Lionel Messi broke two more World Records vs Austria tonight</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/lionel-messi-broke-two-more-world-records-vs-austria-tonight</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Argentina’s 2-0 win over Austria took them through to the round of 32 and all but confirmed them as the winners of Group J.  World Cup 2026 has so far</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Irrepressible Messi breaks World Cup scoring record as Argentina beat Austria</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/argentina-austria-world-cup-group-j-match-report</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>It had to be Lionel Messi, it had to be on this day and perhaps it even needed to be in Dallas too. History was created in the way he knows best, a cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria prediction: Will Lionel Messi continue his devastating World Cup 2026 start?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 15</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/argentina-vs-austria-prediction-will-lionel-messi-continue-his-devastating-world-cup-2026-start</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Is anyone surprised? Argentina started their World Cup campaign with Lionel Messi centre of attention. Business as usual.  It was the no.10’s show in </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Is Lionel Messi injured for Argentina vs Austria? World Cup star’s fitness latest</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>fourfourtwo</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 09</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://www.fourfourtwo.com/person/player/is-lionel-messi-injured-for-argentina-vs-austria-world-cup-stars-fitness-latest</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">Lionel Messi has already caused a stir at World Cup 2026.  He needed just 76 minutes of this summer’s tournament to complete a hat-trick of finishes, </t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>基本确定J组第1！阿根廷淘汰赛大概率踢H组第2，碰佛得角/沙特？</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-06-23 04:24:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a39953d6ee7anative.htm</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>J组积分榜：阿根廷两连胜提前出线 约旦不胜则阿根廷提前锁定头名</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:03:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-23/6a3961a805543native.htm</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TV pundit Bogdanovic apologises for racist comments</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-22T20:07:11</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cvg74ke150zo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Rade Bogdanovic won the German Cup with Werder Bremen in 1999  Former Atletico Madrid and Werder Bremen striker Rade Bogdanovic has apologised for rac</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Argentina vs Austria preview: World Cup Group J at AT&amp;T Stadium</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>sofascore</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>2026-06-22T08:00:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://www.sofascore.com/news/argentina-vs-austria-preview-world-cup-group-j-at-att-stadium</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Argentina face Austria in World Cup Group J at AT&amp;T Stadium. We break down form, trends, projected lineups, odds, and the key Sofascore Rating leaders</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>J组形势：阿根廷赢球即出线！若同时约旦不胜，阿根廷将锁定头名</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>zhibo8</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>2026-06-22 17:50:15</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a37a66c0e83fnative.htm</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>2026-06-22 08:38</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956424</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
 对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>The World Cup records that look set to be broken</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>2026-06-21T13:55:05</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Belgium World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>12 hours ago</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/belgium-world-cup-2026-fixtures-squad-analysis-june-21/</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Belgium are back at the World Cup and desperate to give a much-improved account of themselves on the biggest stage. The Red Devils have got off to a s</t>
         </is>
